--- a/docs/enterprise-context/synthetic/arcturus/15-risk-compliance-register.xlsx
+++ b/docs/enterprise-context/synthetic/arcturus/15-risk-compliance-register.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="300">
   <si>
     <t>Dataset</t>
   </si>
@@ -549,103 +549,106 @@
     <t>CI-APP-SERVICENOW|CI-APP-MUREX</t>
   </si>
   <si>
+    <t>VEN-NCINO</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>RISK-10</t>
+  </si>
+  <si>
+    <t>RISK-011</t>
+  </si>
+  <si>
+    <t>CTRL-110</t>
+  </si>
+  <si>
+    <t>POL-011</t>
+  </si>
+  <si>
+    <t>CI-SEC-OKTA|CI-APP-SAS-MRM</t>
+  </si>
+  <si>
+    <t>VEN-SNOW</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>RISK-11</t>
+  </si>
+  <si>
+    <t>RISK-012</t>
+  </si>
+  <si>
+    <t>CTRL-111</t>
+  </si>
+  <si>
+    <t>POL-012</t>
+  </si>
+  <si>
+    <t>CI-CLOUD-AWS-PROD|CI-APP-WORKDAY-HCM</t>
+  </si>
+  <si>
+    <t>VEN-MICROSOFT</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>RISK-12</t>
+  </si>
+  <si>
+    <t>RISK-013</t>
+  </si>
+  <si>
+    <t>CTRL-112</t>
+  </si>
+  <si>
+    <t>POL-013</t>
+  </si>
+  <si>
+    <t>CI-CLOUD-AZURE-PROD|CI-APP-001</t>
+  </si>
+  <si>
+    <t>VEN-AWS</t>
+  </si>
+  <si>
+    <t>RISK-13</t>
+  </si>
+  <si>
+    <t>RISK-014</t>
+  </si>
+  <si>
+    <t>CTRL-113</t>
+  </si>
+  <si>
+    <t>POL-014</t>
+  </si>
+  <si>
+    <t>CI-APP-MUREX|CI-SVC-002</t>
+  </si>
+  <si>
+    <t>VEN-AZURE</t>
+  </si>
+  <si>
+    <t>RISK-14</t>
+  </si>
+  <si>
+    <t>RISK-015</t>
+  </si>
+  <si>
+    <t>CTRL-114</t>
+  </si>
+  <si>
+    <t>POL-015</t>
+  </si>
+  <si>
+    <t>CI-APP-SAS-MRM|CI-DATA-003</t>
+  </si>
+  <si>
     <t>VEN-DATABRICKS</t>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>RISK-10</t>
-  </si>
-  <si>
-    <t>RISK-011</t>
-  </si>
-  <si>
-    <t>CTRL-110</t>
-  </si>
-  <si>
-    <t>POL-011</t>
-  </si>
-  <si>
-    <t>CI-SEC-OKTA|CI-APP-SAS-MRM</t>
-  </si>
-  <si>
-    <t>VEN-SNOW</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>RISK-11</t>
-  </si>
-  <si>
-    <t>RISK-012</t>
-  </si>
-  <si>
-    <t>CTRL-111</t>
-  </si>
-  <si>
-    <t>POL-012</t>
-  </si>
-  <si>
-    <t>CI-CLOUD-AWS-PROD|CI-APP-WORKDAY-HCM</t>
-  </si>
-  <si>
-    <t>VEN-MICROSOFT</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>RISK-12</t>
-  </si>
-  <si>
-    <t>RISK-013</t>
-  </si>
-  <si>
-    <t>CTRL-112</t>
-  </si>
-  <si>
-    <t>POL-013</t>
-  </si>
-  <si>
-    <t>CI-CLOUD-AZURE-PROD|CI-APP-001</t>
-  </si>
-  <si>
-    <t>VEN-AWS</t>
-  </si>
-  <si>
-    <t>RISK-13</t>
-  </si>
-  <si>
-    <t>RISK-014</t>
-  </si>
-  <si>
-    <t>CTRL-113</t>
-  </si>
-  <si>
-    <t>POL-014</t>
-  </si>
-  <si>
-    <t>CI-APP-MUREX|CI-SVC-002</t>
-  </si>
-  <si>
-    <t>VEN-AZURE</t>
-  </si>
-  <si>
-    <t>RISK-14</t>
-  </si>
-  <si>
-    <t>RISK-015</t>
-  </si>
-  <si>
-    <t>CTRL-114</t>
-  </si>
-  <si>
-    <t>POL-015</t>
-  </si>
-  <si>
-    <t>CI-APP-SAS-MRM|CI-DATA-003</t>
   </si>
   <si>
     <t>RISK-15</t>
@@ -2705,7 +2708,7 @@
         <v>210</v>
       </c>
       <c r="K16" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="L16" t="s">
         <v>117</v>
@@ -2717,7 +2720,7 @@
         <v>95</v>
       </c>
       <c r="O16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P16" t="s">
         <v>97</v>
@@ -2737,7 +2740,7 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B17" t="s">
         <v>120</v>
@@ -2746,10 +2749,10 @@
         <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F17" t="s">
         <v>143</v>
@@ -2764,10 +2767,10 @@
         <v>45</v>
       </c>
       <c r="J17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L17" t="s">
         <v>127</v>
@@ -2779,7 +2782,7 @@
         <v>95</v>
       </c>
       <c r="O17" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P17" t="s">
         <v>97</v>
@@ -2799,7 +2802,7 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B18" t="s">
         <v>130</v>
@@ -2808,10 +2811,10 @@
         <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F18" t="s">
         <v>152</v>
@@ -2826,10 +2829,10 @@
         <v>90</v>
       </c>
       <c r="J18" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L18" t="s">
         <v>137</v>
@@ -2841,7 +2844,7 @@
         <v>95</v>
       </c>
       <c r="O18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P18" t="s">
         <v>97</v>
@@ -2861,7 +2864,7 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B19" t="s">
         <v>140</v>
@@ -2870,10 +2873,10 @@
         <v>121</v>
       </c>
       <c r="D19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E19" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F19" t="s">
         <v>160</v>
@@ -2888,10 +2891,10 @@
         <v>45</v>
       </c>
       <c r="J19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K19" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L19" t="s">
         <v>146</v>
@@ -2903,7 +2906,7 @@
         <v>95</v>
       </c>
       <c r="O19" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P19" t="s">
         <v>97</v>
@@ -2923,7 +2926,7 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s">
         <v>84</v>
@@ -2932,10 +2935,10 @@
         <v>131</v>
       </c>
       <c r="D20" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E20" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F20" t="s">
         <v>168</v>
@@ -2950,10 +2953,10 @@
         <v>45</v>
       </c>
       <c r="J20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L20" t="s">
         <v>155</v>
@@ -2965,7 +2968,7 @@
         <v>95</v>
       </c>
       <c r="O20" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P20" t="s">
         <v>97</v>
@@ -2985,7 +2988,7 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s">
         <v>100</v>
@@ -2994,10 +2997,10 @@
         <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E21" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F21" t="s">
         <v>176</v>
@@ -3012,10 +3015,10 @@
         <v>45</v>
       </c>
       <c r="J21" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K21" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L21" t="s">
         <v>163</v>
@@ -3027,7 +3030,7 @@
         <v>95</v>
       </c>
       <c r="O21" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P21" t="s">
         <v>97</v>
@@ -3047,7 +3050,7 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s">
         <v>110</v>
@@ -3056,10 +3059,10 @@
         <v>149</v>
       </c>
       <c r="D22" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F22" t="s">
         <v>88</v>
@@ -3074,10 +3077,10 @@
         <v>90</v>
       </c>
       <c r="J22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K22" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L22" t="s">
         <v>171</v>
@@ -3089,7 +3092,7 @@
         <v>95</v>
       </c>
       <c r="O22" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P22" t="s">
         <v>97</v>
@@ -3109,7 +3112,7 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B23" t="s">
         <v>120</v>
@@ -3118,10 +3121,10 @@
         <v>85</v>
       </c>
       <c r="D23" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E23" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F23" t="s">
         <v>104</v>
@@ -3136,10 +3139,10 @@
         <v>45</v>
       </c>
       <c r="J23" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K23" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L23" t="s">
         <v>179</v>
@@ -3151,7 +3154,7 @@
         <v>95</v>
       </c>
       <c r="O23" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P23" t="s">
         <v>97</v>
@@ -3171,7 +3174,7 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s">
         <v>130</v>
@@ -3180,10 +3183,10 @@
         <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F24" t="s">
         <v>114</v>
@@ -3198,10 +3201,10 @@
         <v>45</v>
       </c>
       <c r="J24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L24" t="s">
         <v>186</v>
@@ -3213,7 +3216,7 @@
         <v>95</v>
       </c>
       <c r="O24" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P24" t="s">
         <v>97</v>
@@ -3233,7 +3236,7 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B25" t="s">
         <v>140</v>
@@ -3242,10 +3245,10 @@
         <v>111</v>
       </c>
       <c r="D25" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E25" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F25" t="s">
         <v>124</v>
@@ -3260,10 +3263,10 @@
         <v>45</v>
       </c>
       <c r="J25" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K25" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L25" t="s">
         <v>193</v>
@@ -3275,7 +3278,7 @@
         <v>95</v>
       </c>
       <c r="O25" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P25" t="s">
         <v>97</v>
@@ -3295,7 +3298,7 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s">
         <v>84</v>
@@ -3304,10 +3307,10 @@
         <v>121</v>
       </c>
       <c r="D26" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E26" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F26" t="s">
         <v>134</v>
@@ -3322,10 +3325,10 @@
         <v>90</v>
       </c>
       <c r="J26" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K26" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L26" t="s">
         <v>93</v>
@@ -3337,7 +3340,7 @@
         <v>95</v>
       </c>
       <c r="O26" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P26" t="s">
         <v>97</v>
@@ -3357,7 +3360,7 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s">
         <v>100</v>
@@ -3366,10 +3369,10 @@
         <v>131</v>
       </c>
       <c r="D27" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E27" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F27" t="s">
         <v>143</v>
@@ -3384,10 +3387,10 @@
         <v>45</v>
       </c>
       <c r="J27" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K27" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L27" t="s">
         <v>107</v>
@@ -3399,7 +3402,7 @@
         <v>95</v>
       </c>
       <c r="O27" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P27" t="s">
         <v>97</v>
@@ -3419,7 +3422,7 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s">
         <v>110</v>
@@ -3428,10 +3431,10 @@
         <v>26</v>
       </c>
       <c r="D28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F28" t="s">
         <v>152</v>
@@ -3446,10 +3449,10 @@
         <v>45</v>
       </c>
       <c r="J28" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K28" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L28" t="s">
         <v>117</v>
@@ -3461,7 +3464,7 @@
         <v>95</v>
       </c>
       <c r="O28" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P28" t="s">
         <v>97</v>
@@ -3481,7 +3484,7 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s">
         <v>120</v>
@@ -3490,10 +3493,10 @@
         <v>149</v>
       </c>
       <c r="D29" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E29" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F29" t="s">
         <v>160</v>
@@ -3508,7 +3511,7 @@
         <v>45</v>
       </c>
       <c r="J29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K29" t="s">
         <v>92</v>
@@ -3523,7 +3526,7 @@
         <v>95</v>
       </c>
       <c r="O29" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P29" t="s">
         <v>97</v>
@@ -3543,7 +3546,7 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s">
         <v>130</v>
@@ -3552,10 +3555,10 @@
         <v>85</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F30" t="s">
         <v>168</v>
@@ -3570,7 +3573,7 @@
         <v>90</v>
       </c>
       <c r="J30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K30" t="s">
         <v>106</v>
@@ -3585,7 +3588,7 @@
         <v>95</v>
       </c>
       <c r="O30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P30" t="s">
         <v>97</v>
@@ -3605,7 +3608,7 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s">
         <v>140</v>
@@ -3614,10 +3617,10 @@
         <v>101</v>
       </c>
       <c r="D31" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E31" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F31" t="s">
         <v>176</v>
@@ -3632,7 +3635,7 @@
         <v>45</v>
       </c>
       <c r="J31" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K31" t="s">
         <v>116</v>
@@ -3647,7 +3650,7 @@
         <v>95</v>
       </c>
       <c r="O31" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P31" t="s">
         <v>97</v>
